--- a/source/Hoyeh Menu Latest Updated.xlsx
+++ b/source/Hoyeh Menu Latest Updated.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/chef_hoyeh_jrgroup_com_sg/Documents/Desktop/RWS Mob/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Pictures\Hoyeh\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{6D25B51A-1DCB-42C8-A4D5-FF8B07DD812E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1798B815-4344-4C6A-9FFA-D0404621104A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="531">
   <si>
     <t>Meal</t>
   </si>
@@ -377,9 +366,6 @@
     <t xml:space="preserve">Vegetarian </t>
   </si>
   <si>
-    <t>Fried Egg Noodle</t>
-  </si>
-  <si>
     <t>Chee Chong Fan</t>
   </si>
   <si>
@@ -410,9 +396,6 @@
     <t>Nasi Bryani</t>
   </si>
   <si>
-    <t>Steamed Soy Fish</t>
-  </si>
-  <si>
     <t>Black Pepper Fish</t>
   </si>
   <si>
@@ -431,16 +414,10 @@
     <t>Bitter Melon with Black Bean</t>
   </si>
   <si>
-    <t>Garlic Stir Fried Cai Sim</t>
-  </si>
-  <si>
     <t>Pickled Mustard Greens</t>
   </si>
   <si>
     <t>Chicken Rice</t>
-  </si>
-  <si>
-    <t>Lemon Pepper Fish</t>
   </si>
   <si>
     <t>Fish Curry</t>
@@ -806,9 +783,6 @@
     <t xml:space="preserve">Nonya Pork Rendang </t>
   </si>
   <si>
-    <t xml:space="preserve">Baked Chicken with Dang gui  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Crispy Chicken Cutlet </t>
   </si>
   <si>
@@ -863,12 +837,6 @@
     <t>Soya Duck Rice</t>
   </si>
   <si>
-    <t>Curry Bun</t>
-  </si>
-  <si>
-    <t>Teriyaki Chicken Garlic Rice</t>
-  </si>
-  <si>
     <t>Hainanese Chicken Rice</t>
   </si>
   <si>
@@ -914,15 +882,6 @@
     <t>Teriyaki Beef</t>
   </si>
   <si>
-    <t xml:space="preserve">Fried Thai StyleTofu </t>
-  </si>
-  <si>
-    <t>Stir Fry Long Bean with Chilli</t>
-  </si>
-  <si>
-    <t>Braised Cabbage with Mushrooms</t>
-  </si>
-  <si>
     <t>Kai Lan with Garlic in Oyster Sauce</t>
   </si>
   <si>
@@ -1244,9 +1203,6 @@
     <t>Fish Dumpling Noodle</t>
   </si>
   <si>
-    <t>Sweet &amp; SourVeg Chicken</t>
-  </si>
-  <si>
     <t>Gong Poh Chicken</t>
   </si>
   <si>
@@ -1295,15 +1251,9 @@
     <t>Sambal Egg</t>
   </si>
   <si>
-    <t>Sweet Corn Soup</t>
-  </si>
-  <si>
     <t>Ice Cream</t>
   </si>
   <si>
-    <t>Red Bean Longan Soup</t>
-  </si>
-  <si>
     <t>Hainanese Curry Rice</t>
   </si>
   <si>
@@ -1317,9 +1267,6 @@
   </si>
   <si>
     <t>Jing Du Pork Rib</t>
-  </si>
-  <si>
-    <t>Sez Chuan Steamed Tofu</t>
   </si>
   <si>
     <t>Fu Yong Egg</t>
@@ -1666,6 +1613,80 @@
   </si>
   <si>
     <t>Bian Xiang</t>
+  </si>
+  <si>
+    <t>White/ Wholemeal Bread w Assorted Spreads
+白面包/全麦面包配多种抹酱</t>
+  </si>
+  <si>
+    <t>Ipoh Hor Fun 怡保河粉</t>
+  </si>
+  <si>
+    <t>Curry Bun 咖喱面包</t>
+  </si>
+  <si>
+    <t>Egg 鸡蛋</t>
+  </si>
+  <si>
+    <t>Fried Egg Noodle 炒蛋面</t>
+  </si>
+  <si>
+    <t>Assorted Cereal w Milk 什锦麦片配牛奶</t>
+  </si>
+  <si>
+    <t>Teriyaki Chicken Garlic Rice 蒜香照烧鸡肉饭</t>
+  </si>
+  <si>
+    <t>Braised Pork Belly 红烧肉</t>
+  </si>
+  <si>
+    <t>Steamed Soy Fish 豉油蒸鱼</t>
+  </si>
+  <si>
+    <t>Sweet &amp; SourVeg Chicken 酸甜素鸡</t>
+  </si>
+  <si>
+    <t>Kai Lan with Oyster Sauce 蚝油芥兰</t>
+  </si>
+  <si>
+    <t>Garlic Stir Fried Cai Sim 蒜蓉炒菜心</t>
+  </si>
+  <si>
+    <t>Fried Thai StyleTofu 泰式炸豆腐</t>
+  </si>
+  <si>
+    <t>4 x Salads (Honey Mustard and Vinaigrette )
+4份沙拉（搭配蜂蜜芥末酱与油醋汁）</t>
+  </si>
+  <si>
+    <t>Sweet Corn Soup 玉米汤</t>
+  </si>
+  <si>
+    <t>Red Bean Longan Soup 红豆龙眼汤</t>
+  </si>
+  <si>
+    <t>Lor Mee 卤面</t>
+  </si>
+  <si>
+    <t>Nasi Padang 巴东饭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baked Chicken with Dang gui 当归烤鸡  </t>
+  </si>
+  <si>
+    <t>Lemon Pepper Fish 柠檬椒盐鱼</t>
+  </si>
+  <si>
+    <t>Sez Chuan Steamed Tofu 川味蒸豆腐</t>
+  </si>
+  <si>
+    <t>Braised Cabbage with Mushrooms 香菇焖白菜</t>
+  </si>
+  <si>
+    <t>Stir Fry Long Bean with Chilli 辣炒长豆</t>
+  </si>
+  <si>
+    <t>Luncheon Meat 午餐肉</t>
   </si>
 </sst>
 </file>
@@ -2245,7 +2266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2527,6 +2548,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2864,15 +2888,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3331950C-5F09-41DF-8A79-5F2EED696A70}">
   <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="75"/>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -2883,7 +2907,7 @@
       <c r="H1" s="76"/>
       <c r="I1" s="77"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
@@ -2910,7 +2934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="3">
@@ -2935,7 +2959,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
         <v>8</v>
       </c>
@@ -2964,7 +2988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="25" t="s">
         <v>9</v>
@@ -2991,34 +3015,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83"/>
       <c r="B6" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="25" t="s">
         <v>23</v>
@@ -3027,7 +3051,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>34</v>
@@ -3036,22 +3060,22 @@
         <v>35</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I7" s="29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="84"/>
       <c r="B8" s="30" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D8" s="31" t="s">
         <v>37</v>
@@ -3060,19 +3084,19 @@
         <v>38</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
@@ -3086,10 +3110,10 @@
         <v>41</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>42</v>
@@ -3101,7 +3125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="86"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
@@ -3116,50 +3140,50 @@
         <v>46</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>47</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="86"/>
       <c r="B11" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G11" s="21" t="s">
         <v>51</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="86"/>
       <c r="B12" s="73"/>
       <c r="C12" s="20" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D12" s="63" t="s">
         <v>52</v>
@@ -3174,17 +3198,17 @@
         <v>54</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="86"/>
       <c r="B13" s="73"/>
       <c r="C13" s="20" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D13" s="63" t="s">
         <v>56</v>
@@ -3193,19 +3217,19 @@
         <v>57</v>
       </c>
       <c r="F13" s="55" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>58</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="86"/>
       <c r="B14" s="73"/>
       <c r="C14" s="20" t="s">
@@ -3215,22 +3239,22 @@
         <v>60</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="86"/>
       <c r="B15" s="73"/>
       <c r="C15" s="20" t="s">
@@ -3240,22 +3264,22 @@
         <v>63</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="86"/>
       <c r="B16" s="88"/>
       <c r="C16" s="20" t="s">
@@ -3271,16 +3295,16 @@
         <v>67</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="I16" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="86"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
@@ -3307,13 +3331,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="86"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D18" s="63" t="s">
         <v>79</v>
@@ -3322,19 +3346,19 @@
         <v>80</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>81</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="87"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
@@ -3343,25 +3367,25 @@
         <v>82</v>
       </c>
       <c r="D19" s="64" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E19" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G19" s="39" t="s">
         <v>82</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I19" s="40" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="89" t="s">
         <v>15</v>
       </c>
@@ -3372,7 +3396,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="65" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E20" s="22" t="s">
         <v>83</v>
@@ -3381,16 +3405,16 @@
         <v>19</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
@@ -3402,49 +3426,49 @@
         <v>86</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="89"/>
       <c r="B22" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D22" s="63" t="s">
         <v>88</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89"/>
       <c r="B23" s="73"/>
       <c r="C23" s="32" t="s">
@@ -3454,13 +3478,13 @@
         <v>90</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="H23" s="18" t="s">
         <v>91</v>
@@ -3469,7 +3493,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="89"/>
       <c r="B24" s="73"/>
       <c r="C24" s="32" t="s">
@@ -3491,35 +3515,35 @@
         <v>98</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="89"/>
       <c r="B25" s="73"/>
       <c r="C25" s="20" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="G25" s="21" t="s">
         <v>99</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="89"/>
       <c r="B26" s="73"/>
       <c r="C26" s="20" t="s">
@@ -3529,7 +3553,7 @@
         <v>101</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>102</v>
@@ -3538,13 +3562,13 @@
         <v>103</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="88"/>
       <c r="C27" s="20" t="s">
@@ -3557,10 +3581,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>105</v>
@@ -3569,7 +3593,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="89"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
@@ -3596,13 +3620,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="89"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D29" s="63" t="s">
         <v>79</v>
@@ -3611,19 +3635,19 @@
         <v>80</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>81</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
@@ -3632,25 +3656,25 @@
         <v>82</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E30" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G30" s="39" t="s">
         <v>82</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I30" s="40" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="91" t="s">
         <v>16</v>
       </c>
@@ -3664,10 +3688,10 @@
         <v>41</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F31" s="24" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="G31" s="24" t="s">
         <v>42</v>
@@ -3676,10 +3700,10 @@
         <v>43</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="92"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
@@ -3694,50 +3718,50 @@
         <v>46</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="H32" s="18" t="s">
         <v>47</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="92"/>
       <c r="B33" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D33" s="63" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G33" s="21" t="s">
         <v>51</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="92"/>
       <c r="B34" s="73"/>
       <c r="C34" s="20" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D34" s="63" t="s">
         <v>52</v>
@@ -3752,17 +3776,17 @@
         <v>54</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="92"/>
       <c r="B35" s="73"/>
       <c r="C35" s="20" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D35" s="63" t="s">
         <v>56</v>
@@ -3771,19 +3795,19 @@
         <v>57</v>
       </c>
       <c r="F35" s="55" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="H35" s="18" t="s">
         <v>58</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="92"/>
       <c r="B36" s="73"/>
       <c r="C36" s="20" t="s">
@@ -3793,22 +3817,22 @@
         <v>60</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="92"/>
       <c r="B37" s="73"/>
       <c r="C37" s="20" t="s">
@@ -3818,22 +3842,22 @@
         <v>63</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="92"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
@@ -3851,16 +3875,16 @@
         <v>67</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="I38" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="92"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
@@ -3887,13 +3911,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="92"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D40" s="63" t="s">
         <v>79</v>
@@ -3902,19 +3926,19 @@
         <v>80</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G40" s="21" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H40" s="18" t="s">
         <v>81</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -3925,31 +3949,31 @@
         <v>82</v>
       </c>
       <c r="D41" s="64" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E41" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F41" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G41" s="39" t="s">
         <v>82</v>
       </c>
       <c r="H41" s="39" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="I41" s="40" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="9"/>
       <c r="E42" s="10"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="11"/>
@@ -3960,7 +3984,7 @@
       <c r="H43" s="12"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="11"/>
@@ -3971,15 +3995,15 @@
       <c r="H44" s="12"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
@@ -3990,7 +4014,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -4001,7 +4025,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="8"/>
@@ -4012,7 +4036,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="11"/>
@@ -4023,7 +4047,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -4034,12 +4058,12 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="G52" s="10"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="11"/>
@@ -4050,15 +4074,15 @@
       <c r="H53" s="12"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -4069,27 +4093,27 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="11"/>
@@ -4100,7 +4124,7 @@
       <c r="H61" s="12"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="11"/>
@@ -4111,15 +4135,15 @@
       <c r="H62" s="12"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -4130,7 +4154,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -4141,7 +4165,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -4152,7 +4176,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -4163,7 +4187,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -4174,7 +4198,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -4185,7 +4209,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -4196,7 +4220,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="11"/>
@@ -4207,7 +4231,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="11"/>
@@ -4218,7 +4242,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -4229,7 +4253,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -4240,7 +4264,7 @@
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="74"/>
@@ -4251,7 +4275,7 @@
       <c r="H76" s="74"/>
       <c r="I76" s="74"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="74"/>
@@ -4263,7 +4287,7 @@
       <c r="I77" s="74"/>
       <c r="J77" s="74"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -4274,7 +4298,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="6"/>
@@ -4285,19 +4309,19 @@
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="16"/>
       <c r="B83" s="16"/>
     </row>
@@ -4325,15 +4349,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF35105-E78C-446D-B499-ECA475F17C6E}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="75"/>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -4344,7 +4368,7 @@
       <c r="H1" s="76"/>
       <c r="I1" s="77"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
@@ -4371,7 +4395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="3">
@@ -4396,7 +4420,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
         <v>8</v>
       </c>
@@ -4404,7 +4428,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>22</v>
+        <v>507</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>22</v>
@@ -4425,13 +4449,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>29</v>
+      <c r="C5" s="97" t="s">
+        <v>512</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>29</v>
@@ -4452,40 +4476,40 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="49" t="s">
+        <v>511</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>113</v>
-      </c>
       <c r="E6" s="21" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>31</v>
+        <v>510</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>37</v>
@@ -4494,46 +4518,46 @@
         <v>26</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G7" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>115</v>
-      </c>
       <c r="I7" s="29" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="84"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>253</v>
+        <v>509</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F8" s="31" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H8" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="H8" s="31" t="s">
-        <v>118</v>
-      </c>
       <c r="I8" s="36" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
@@ -4541,213 +4565,213 @@
         <v>49</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>119</v>
+        <v>508</v>
       </c>
       <c r="D9" s="43" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F9" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="H9" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="H9" s="43" t="s">
-        <v>121</v>
-      </c>
       <c r="I9" s="45" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="86"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>254</v>
+        <v>513</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>109</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="86"/>
       <c r="B11" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>308</v>
+        <v>514</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="86"/>
       <c r="B12" s="73"/>
       <c r="C12" s="20" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="86"/>
       <c r="B13" s="73"/>
       <c r="C13" s="20" t="s">
+        <v>516</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>391</v>
-      </c>
       <c r="I13" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="86"/>
       <c r="B14" s="73"/>
       <c r="C14" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="I14" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="86"/>
       <c r="B15" s="73"/>
       <c r="C15" s="20" t="s">
-        <v>130</v>
+        <v>518</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="86"/>
       <c r="B16" s="88"/>
       <c r="C16" s="20" t="s">
-        <v>270</v>
+        <v>519</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A17" s="86"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>72</v>
+        <v>520</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>73</v>
@@ -4768,46 +4792,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="86"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>397</v>
+        <v>521</v>
       </c>
       <c r="D18" s="18" t="s">
         <v>110</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="87"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>399</v>
+        <v>522</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F19" s="39" t="s">
         <v>108</v>
@@ -4816,13 +4840,13 @@
         <v>82</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I19" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="93" t="s">
         <v>15</v>
       </c>
@@ -4830,213 +4854,213 @@
         <v>49</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>41</v>
+        <v>523</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="E20" s="43" t="s">
         <v>40</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="H20" s="43" t="s">
         <v>84</v>
       </c>
       <c r="I20" s="45" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>170</v>
+        <v>524</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="89"/>
       <c r="B22" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>234</v>
+        <v>525</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89"/>
       <c r="B23" s="73"/>
       <c r="C23" s="20" t="s">
-        <v>133</v>
+        <v>526</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G23" s="57" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I23" s="29" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="89"/>
       <c r="B24" s="73"/>
       <c r="C24" s="20" t="s">
-        <v>405</v>
+        <v>527</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="89"/>
       <c r="B25" s="73"/>
       <c r="C25" s="20" t="s">
-        <v>272</v>
+        <v>528</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="89"/>
       <c r="B26" s="73"/>
       <c r="C26" s="20" t="s">
-        <v>271</v>
+        <v>529</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>63</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="88"/>
       <c r="C27" s="20" t="s">
-        <v>25</v>
+        <v>530</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>105</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A28" s="89"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>72</v>
+        <v>520</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>73</v>
@@ -5057,46 +5081,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="89"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>397</v>
+        <v>521</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>110</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>399</v>
+        <v>522</v>
       </c>
       <c r="D30" s="31" t="s">
         <v>82</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F30" s="39" t="s">
         <v>108</v>
@@ -5105,13 +5129,13 @@
         <v>82</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I30" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="91" t="s">
         <v>16</v>
       </c>
@@ -5119,188 +5143,188 @@
         <v>49</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>119</v>
+        <v>508</v>
       </c>
       <c r="D31" s="43" t="s">
         <v>19</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="F31" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="H31" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="H31" s="43" t="s">
-        <v>121</v>
-      </c>
       <c r="I31" s="45" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="92"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>254</v>
+        <v>513</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>109</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="92"/>
       <c r="B33" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>308</v>
+        <v>514</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="92"/>
       <c r="B34" s="73"/>
       <c r="C34" s="20" t="s">
-        <v>123</v>
+        <v>515</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="E34" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="92"/>
       <c r="B35" s="73"/>
       <c r="C35" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="I35" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="92"/>
       <c r="B36" s="73"/>
       <c r="C36" s="20" t="s">
-        <v>130</v>
+        <v>518</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="92"/>
       <c r="B37" s="73"/>
       <c r="C37" s="20" t="s">
-        <v>270</v>
+        <v>519</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="92"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>72</v>
+        <v>520</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>73</v>
@@ -5321,46 +5345,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="92"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>397</v>
+        <v>521</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>110</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="92"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>399</v>
+        <v>522</v>
       </c>
       <c r="D40" s="31" t="s">
         <v>82</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F40" s="39" t="s">
         <v>108</v>
@@ -5369,13 +5393,13 @@
         <v>82</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I40" s="36" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="89.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -5383,28 +5407,28 @@
         <v>111</v>
       </c>
       <c r="C41" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="H41" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="I41" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -5415,7 +5439,7 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="11"/>
@@ -5426,15 +5450,15 @@
       <c r="H43" s="12"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -5445,7 +5469,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -5456,7 +5480,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="8"/>
@@ -5467,7 +5491,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -5478,7 +5502,7 @@
       <c r="H49" s="11"/>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="11"/>
@@ -5489,12 +5513,12 @@
       <c r="H50" s="12"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="G51" s="10"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="11"/>
@@ -5505,15 +5529,15 @@
       <c r="H52" s="12"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -5524,27 +5548,27 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -5555,7 +5579,7 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="11"/>
@@ -5566,15 +5590,15 @@
       <c r="H61" s="12"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -5585,7 +5609,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -5596,7 +5620,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -5607,7 +5631,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -5618,7 +5642,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -5629,7 +5653,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -5640,7 +5664,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -5651,7 +5675,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -5662,7 +5686,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="11"/>
@@ -5673,7 +5697,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -5684,7 +5708,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -5695,7 +5719,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="74"/>
@@ -5706,7 +5730,7 @@
       <c r="H75" s="74"/>
       <c r="I75" s="74"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="74"/>
@@ -5718,7 +5742,7 @@
       <c r="I76" s="74"/>
       <c r="J76" s="74"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -5729,7 +5753,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -5740,19 +5764,19 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
     </row>
@@ -5780,15 +5804,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFDDF52-516B-4631-A9D2-1246E2DB53C6}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="75"/>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -5799,7 +5823,7 @@
       <c r="H1" s="76"/>
       <c r="I1" s="77"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
@@ -5826,7 +5850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="3">
@@ -5851,7 +5875,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
         <v>8</v>
       </c>
@@ -5880,7 +5904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
@@ -5907,34 +5931,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
@@ -5952,43 +5976,43 @@
         <v>39</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="84"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="D8" s="31" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
@@ -5996,207 +6020,207 @@
         <v>49</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="I9" s="45" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="86"/>
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="86"/>
       <c r="B11" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="86"/>
       <c r="B12" s="73"/>
       <c r="C12" s="32" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="86"/>
       <c r="B13" s="73"/>
       <c r="C13" s="32" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="86"/>
       <c r="B14" s="73"/>
       <c r="C14" s="32" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="86"/>
       <c r="B15" s="73"/>
       <c r="C15" s="32" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="86"/>
       <c r="B16" s="88"/>
       <c r="C16" s="32" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="86"/>
       <c r="B17" s="18" t="s">
         <v>70</v>
@@ -6223,34 +6247,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="86"/>
       <c r="B18" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>107</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="87"/>
       <c r="B19" s="39" t="s">
         <v>71</v>
@@ -6259,13 +6283,13 @@
         <v>82</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>82</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="G19" s="31" t="s">
         <v>82</v>
@@ -6277,7 +6301,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="93" t="s">
         <v>15</v>
       </c>
@@ -6285,157 +6309,157 @@
         <v>49</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H20" s="43" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="I20" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89"/>
       <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="I21" s="67" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="89"/>
       <c r="B22" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89"/>
       <c r="B23" s="73"/>
       <c r="C23" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>175</v>
-      </c>
       <c r="I23" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="89"/>
       <c r="B24" s="73"/>
       <c r="C24" s="32" t="s">
         <v>59</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="E24" s="21" t="s">
         <v>95</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="89"/>
       <c r="B25" s="73"/>
       <c r="C25" s="32" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="89"/>
       <c r="B26" s="73"/>
       <c r="C26" s="32" t="s">
@@ -6448,44 +6472,44 @@
         <v>64</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="88"/>
       <c r="C27" s="32" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>104</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="I27" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="89"/>
       <c r="B28" s="18" t="s">
         <v>70</v>
@@ -6512,34 +6536,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="89"/>
       <c r="B29" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F29" s="18" t="s">
         <v>107</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="39" t="s">
         <v>71</v>
@@ -6548,13 +6572,13 @@
         <v>82</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="E30" s="31" t="s">
         <v>82</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>82</v>
@@ -6566,7 +6590,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="91" t="s">
         <v>16</v>
       </c>
@@ -6574,182 +6598,182 @@
         <v>49</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="H31" s="43" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="92"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="92"/>
       <c r="B33" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="92"/>
       <c r="B34" s="73"/>
       <c r="C34" s="32" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="92"/>
       <c r="B35" s="73"/>
       <c r="C35" s="32" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="92"/>
       <c r="B36" s="73"/>
       <c r="C36" s="32" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="92"/>
       <c r="B37" s="73"/>
       <c r="C37" s="32" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D37" s="21" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="92"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
@@ -6776,34 +6800,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="92"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>107</v>
       </c>
       <c r="G39" s="21" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H39" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="92"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
@@ -6812,13 +6836,13 @@
         <v>82</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="E40" s="31" t="s">
         <v>82</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>82</v>
@@ -6830,7 +6854,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="150.44999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -6838,28 +6862,28 @@
         <v>111</v>
       </c>
       <c r="C41" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="61" t="s">
         <v>180</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="H41" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="E41" s="31" t="s">
+      <c r="I41" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="F41" s="58" t="s">
-        <v>183</v>
-      </c>
-      <c r="G41" s="61" t="s">
-        <v>184</v>
-      </c>
-      <c r="H41" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="I41" s="59" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -6870,15 +6894,15 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -6889,7 +6913,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -6900,7 +6924,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -6911,7 +6935,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="11"/>
@@ -6922,7 +6946,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -6933,12 +6957,12 @@
       <c r="H49" s="12"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -6949,15 +6973,15 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -6968,27 +6992,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="11"/>
@@ -6999,7 +7023,7 @@
       <c r="H59" s="12"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -7010,15 +7034,15 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="11"/>
@@ -7029,7 +7053,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -7040,7 +7064,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -7051,7 +7075,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -7062,7 +7086,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -7073,7 +7097,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -7084,7 +7108,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -7095,7 +7119,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -7106,7 +7130,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -7117,7 +7141,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -7128,7 +7152,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -7139,7 +7163,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="74"/>
@@ -7150,7 +7174,7 @@
       <c r="H74" s="74"/>
       <c r="I74" s="74"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="74"/>
@@ -7162,7 +7186,7 @@
       <c r="I75" s="74"/>
       <c r="J75" s="74"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -7173,7 +7197,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -7184,19 +7208,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
     </row>
@@ -7224,15 +7248,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29988196-DFEB-46AE-A95C-9191B0B4EB55}">
   <dimension ref="A1:J81"/>
-  <sheetFormatPr defaultColWidth="28.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="28.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="47.453125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="18.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="47.44140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="47.77734375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="25.8" x14ac:dyDescent="0.3">
       <c r="A1" s="75"/>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -7243,7 +7267,7 @@
       <c r="H1" s="76"/>
       <c r="I1" s="77"/>
     </row>
-    <row r="2" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
@@ -7270,7 +7294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="3">
@@ -7295,7 +7319,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
         <v>8</v>
       </c>
@@ -7324,7 +7348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="51" t="s">
         <v>9</v>
@@ -7351,34 +7375,34 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83"/>
       <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>229</v>
-      </c>
       <c r="F6" s="18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="51" t="s">
         <v>23</v>
@@ -7399,13 +7423,13 @@
         <v>31</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="84"/>
       <c r="B8" s="53" t="s">
         <v>11</v>
@@ -7414,25 +7438,25 @@
         <v>28</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F8" s="39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G8" s="39" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I8" s="40" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="85" t="s">
         <v>12</v>
       </c>
@@ -7440,198 +7464,198 @@
         <v>49</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="I9" s="45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="86"/>
       <c r="B10" s="69" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F10" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="G10" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>502</v>
-      </c>
       <c r="I10" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="86"/>
       <c r="B11" s="94" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="86"/>
       <c r="B12" s="95"/>
       <c r="C12" s="20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D12" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="86"/>
       <c r="B13" s="95"/>
       <c r="C13" s="20" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="86"/>
       <c r="B14" s="95"/>
       <c r="C14" s="20" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="86"/>
       <c r="B15" s="95"/>
       <c r="C15" s="20" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>63</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="86"/>
       <c r="B16" s="96"/>
       <c r="C16" s="20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>69</v>
@@ -7640,7 +7664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="86"/>
       <c r="B17" s="69" t="s">
         <v>70</v>
@@ -7667,34 +7691,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="86"/>
       <c r="B18" s="69" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E18" s="18" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="87"/>
       <c r="B19" s="70" t="s">
         <v>71</v>
@@ -7703,13 +7727,13 @@
         <v>82</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G19" s="31" t="s">
         <v>82</v>
@@ -7721,7 +7745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="93" t="s">
         <v>15</v>
       </c>
@@ -7729,207 +7753,207 @@
         <v>49</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="D20" s="43" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="H20" s="43" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="45" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="89"/>
       <c r="B21" s="69" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>87</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="89"/>
       <c r="B22" s="94" t="s">
         <v>48</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="89"/>
       <c r="B23" s="95"/>
       <c r="C23" s="20" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="89"/>
       <c r="B24" s="95"/>
       <c r="C24" s="20" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="89"/>
       <c r="B25" s="95"/>
       <c r="C25" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D25" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="I25" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="89"/>
       <c r="B26" s="95"/>
       <c r="C26" s="20" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="89"/>
       <c r="B27" s="96"/>
       <c r="C27" s="20" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>104</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="89"/>
       <c r="B28" s="69" t="s">
         <v>70</v>
@@ -7956,34 +7980,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="89"/>
       <c r="B29" s="69" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G29" s="21" t="s">
         <v>30</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="90"/>
       <c r="B30" s="70" t="s">
         <v>71</v>
@@ -7992,13 +8016,13 @@
         <v>82</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E30" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>82</v>
@@ -8010,7 +8034,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="91" t="s">
         <v>16</v>
       </c>
@@ -8018,173 +8042,173 @@
         <v>49</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D31" s="43" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="H31" s="43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I31" s="45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="92"/>
       <c r="B32" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="E32" s="71" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="F32" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="H32" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="G32" s="21" t="s">
-        <v>491</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>502</v>
-      </c>
       <c r="I32" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="92"/>
       <c r="B33" s="72" t="s">
         <v>48</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="92"/>
       <c r="B34" s="73"/>
       <c r="C34" s="20" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D34" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="I34" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="92"/>
       <c r="B35" s="73"/>
       <c r="C35" s="20" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>61</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="92"/>
       <c r="B36" s="73"/>
       <c r="C36" s="20" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>63</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="92"/>
       <c r="B37" s="73"/>
       <c r="C37" s="20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>69</v>
@@ -8193,7 +8217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="92"/>
       <c r="B38" s="18" t="s">
         <v>70</v>
@@ -8220,34 +8244,34 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="92"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="E39" s="18" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="G39" s="21" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="92"/>
       <c r="B40" s="18" t="s">
         <v>71</v>
@@ -8256,13 +8280,13 @@
         <v>82</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="E40" s="39" t="s">
         <v>82</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>82</v>
@@ -8274,7 +8298,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" s="7" customFormat="1" ht="119.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="46" t="s">
         <v>14</v>
       </c>
@@ -8282,28 +8306,28 @@
         <v>111</v>
       </c>
       <c r="C41" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="H41" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="I41" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="F41" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="I41" s="40" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="11"/>
@@ -8314,15 +8338,15 @@
       <c r="H42" s="12"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
-    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
     </row>
-    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -8333,7 +8357,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="8"/>
@@ -8344,7 +8368,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="8"/>
@@ -8355,7 +8379,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="11"/>
@@ -8366,7 +8390,7 @@
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="11"/>
@@ -8377,12 +8401,12 @@
       <c r="H49" s="12"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="11"/>
@@ -8393,15 +8417,15 @@
       <c r="H51" s="12"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
     </row>
-    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
     </row>
-    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -8412,27 +8436,27 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="11"/>
@@ -8443,7 +8467,7 @@
       <c r="H59" s="12"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="11"/>
@@ -8454,15 +8478,15 @@
       <c r="H60" s="12"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
     </row>
-    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
     </row>
-    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="11"/>
@@ -8473,7 +8497,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="11"/>
@@ -8484,7 +8508,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="11"/>
@@ -8495,7 +8519,7 @@
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="11"/>
@@ -8506,7 +8530,7 @@
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="11"/>
@@ -8517,7 +8541,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="11"/>
@@ -8528,7 +8552,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="11"/>
@@ -8539,7 +8563,7 @@
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="11"/>
@@ -8550,7 +8574,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="11"/>
@@ -8561,7 +8585,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -8572,7 +8596,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -8583,7 +8607,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="74"/>
@@ -8594,7 +8618,7 @@
       <c r="H74" s="74"/>
       <c r="I74" s="74"/>
     </row>
-    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="74"/>
@@ -8606,7 +8630,7 @@
       <c r="I75" s="74"/>
       <c r="J75" s="74"/>
     </row>
-    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -8617,7 +8641,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
     </row>
-    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -8628,19 +8652,19 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="16"/>
       <c r="B81" s="16"/>
     </row>
